--- a/task5_full_pipeline_clean.xlsx
+++ b/task5_full_pipeline_clean.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -760,37 +760,69 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2025-03-25</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Волков Игорь</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>79998889900</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>XTA888888888</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Детейлинг</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
         <v>10</v>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>2025-03-31</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Морозова Елена</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>79999990011</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>XTA999999999</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>Кузовной ремонт</t>
         </is>
       </c>
-      <c r="G10" t="n">
+      <c r="G11" t="n">
         <v>3500</v>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>in_progress</t>
         </is>
